--- a/tame_output/ON/bt/strategyON_20240404.xlsx
+++ b/tame_output/ON/bt/strategyON_20240404.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.8%</t>
+          <t>112.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.6%</t>
+          <t>129.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-634.3%</t>
+          <t>-624.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.7%</t>
+          <t>-69.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>495.8%</t>
+          <t>500.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-488.9%</t>
+          <t>-488.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-254.1%</t>
+          <t>-250.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>522.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-197.4%</t>
+          <t>-197.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-299.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.1%</t>
+          <t>-162.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-191.1%</t>
+          <t>-192.8%</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-180.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-116.5%</t>
+          <t>-117.5%</t>
         </is>
       </c>
     </row>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.401056963576938</v>
+        <v>-4.302155344464648</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.363292324286261</v>
+        <v>1.402852971931177</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7436077442970859</v>
+        <v>-0.6713044055212015</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.677906887452532</v>
+        <v>2.721288890718063</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.727489492444682</v>
+        <v>-4.628587873332392</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.221004087741254</v>
+        <v>1.26056473538617</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.7537726560283498</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.660092715415865</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.729053643554985</v>
+        <v>-4.630152024442695</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.218959018953099</v>
+        <v>1.258519666598014</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.7537726560283498</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.65867330707183</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.092679888455298</v>
+        <v>-4.993778269343008</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.079996081227215</v>
+        <v>1.11955672887213</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-0.8519942928954756</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.606227885185796</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.09025282392658</v>
+        <v>-4.99135120481429</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.080221422044533</v>
+        <v>1.119782069689449</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9246304134785115</v>
+        <v>-0.8523270747026273</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.561900727841806</v>
+        <v>2.605282731107336</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.498841601107259</v>
+        <v>-5.399939981994968</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9155474551870211</v>
+        <v>0.9551081028319368</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.260915851883306</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.315509005548158</v>
+        <v>2.358891008813688</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.911824085248353</v>
+        <v>-5.812922466136062</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7455398940020439</v>
+        <v>0.7851005416469601</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.260915851883306</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.310694438019619</v>
+        <v>2.354076441285149</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.32821595953535</v>
+        <v>-6.229314340423059</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5769771948961222</v>
+        <v>0.6165378425410384</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.260915851883306</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.308688488628496</v>
+        <v>2.352070491894026</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.704892970065194</v>
+        <v>-6.605991350952904</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4365650813528634</v>
+        <v>0.4761257289977796</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.260915851883306</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.318947179297175</v>
+        <v>2.362329182562705</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.718607834390306</v>
+        <v>-6.619706215278015</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4271787007685144</v>
+        <v>0.4667393484134301</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.260915851883306</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.31504674444287</v>
+        <v>2.358428747708401</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.031432633635285</v>
+        <v>-6.932531014522994</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3004537011255235</v>
+        <v>0.3400143487704392</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.260915851883306</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.313451664497871</v>
+        <v>2.356833667763402</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.036245672100622</v>
+        <v>-6.937344052988331</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3023074616685966</v>
+        <v>0.3418681093135127</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.262462486586092</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.316302659605408</v>
+        <v>2.359684662870938</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.469594780210858</v>
+        <v>-7.370693161098568</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1249415138900991</v>
+        <v>0.1645021615350153</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.262462486586092</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.312276355071005</v>
+        <v>2.355658358336535</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.85259616895349</v>
+        <v>-7.753694549841199</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.02836114292853731</v>
+        <v>0.01119950471637843</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.262462486586092</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.312174253749421</v>
+        <v>2.355556257014951</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.227581495124767</v>
+        <v>-8.128679876012477</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1757837574256182</v>
+        <v>-0.1362231097807021</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.637447812757369</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.089754574018084</v>
+        <v>2.133136577283615</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.587111817628768</v>
+        <v>-8.488210198516478</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3142455831291686</v>
+        <v>-0.2746849354842524</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.637447812757369</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.095104877316134</v>
+        <v>2.138486880581665</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.913511846293781</v>
+        <v>-8.814610227181491</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.4368895746379962</v>
+        <v>-0.3973289269930804</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.036151180198266</v>
+        <v>-1.963847841422382</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.907180880074304</v>
+        <v>1.950562883339835</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.907035699500222</v>
+        <v>-8.808134080387932</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4312573652988037</v>
+        <v>-0.3916967176538875</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.029675033404706</v>
+        <v>-1.957371694628822</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.914108318772209</v>
+        <v>1.95749032203774</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.903344774543811</v>
+        <v>-8.804443155431521</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4297809953162393</v>
+        <v>-0.3902203476713235</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.029675033404706</v>
+        <v>-1.957371694628822</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.914108318772209</v>
+        <v>1.95749032203774</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.107602949873675</v>
+        <v>-9.008701330761385</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.5059710683295426</v>
+        <v>-0.4664104206846265</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.157313978018695</v>
+        <v>-2.085010639242811</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.843038149122458</v>
+        <v>1.886420152387988</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.26824197636204</v>
+        <v>-9.16934035724975</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5657441244404526</v>
+        <v>-0.5261834767955365</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.272047451021091</v>
+        <v>-2.199744112245207</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.778680619805457</v>
+        <v>1.822062623070987</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.194772144694591</v>
+        <v>-9.095870525582301</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5209844902800516</v>
+        <v>-0.4814238426351358</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.198577619353642</v>
+        <v>-2.126274280577758</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.838134220299347</v>
+        <v>1.881516223564877</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.369896562081134</v>
+        <v>-9.270994942968844</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5764790364871524</v>
+        <v>-0.5369183888422362</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.301398697964302</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.747614790614937</v>
+        <v>1.790996793880468</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.604348656095624</v>
+        <v>-9.505447036983334</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.677479038994544</v>
+        <v>-0.6379183913496282</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.301398697964302</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.740395625713341</v>
+        <v>1.783777628978872</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.892152500632863</v>
+        <v>-9.793250881520573</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.7992727675834157</v>
+        <v>-0.7597121199385</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.661505881277424</v>
+        <v>-2.58920254250154</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.561041128217022</v>
+        <v>1.604423131482553</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.12197694779669</v>
+        <v>-10.0230753286844</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8900867566103896</v>
+        <v>-0.8505261089654734</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.824153418347585</v>
+        <v>-2.751850079571701</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.464568395813482</v>
+        <v>1.507950399079013</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.35400586753295</v>
+        <v>-10.25510424842066</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9802045958757799</v>
+        <v>-0.9406439482308637</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.813862776760124</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.430054506129543</v>
+        <v>1.473436509395073</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.30199035356414</v>
+        <v>-10.20308873445185</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9554080546018531</v>
+        <v>-0.9158474069569378</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.813862776760124</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.434044841815944</v>
+        <v>1.477426845081474</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.44366219528826</v>
+        <v>-10.34476057617597</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.013552018190243</v>
+        <v>-0.9739913705453276</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.813862776760124</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.432569614917202</v>
+        <v>1.475951618182733</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.54256893574753</v>
+        <v>-10.44366731663524</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.038061304209081</v>
+        <v>-0.9985006565641652</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.985072855995284</v>
+        <v>-2.912769517219399</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.388278980806509</v>
+        <v>1.43166098407204</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.34341682851043</v>
+        <v>-10.24451520939814</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9714515949609246</v>
+        <v>-0.9318909473160084</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81975033004547</v>
+        <v>-2.747446991269586</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.474421362729714</v>
+        <v>1.517803365995245</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.11757167579102</v>
+        <v>-10.01867005667873</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8715344608369517</v>
+        <v>-0.8319738131920356</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.705520315682422</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.509156441118221</v>
+        <v>1.552538444383752</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.831296863468328</v>
+        <v>-9.732395244356038</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7558853913518151</v>
+        <v>-0.7163247437068989</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.705520315682422</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.51029558567428</v>
+        <v>1.55367758893981</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.884192151512615</v>
+        <v>-9.785290532400325</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7744097324074222</v>
+        <v>-0.734849084762506</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.772868308369861</v>
+        <v>-2.700564969593976</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.515902567489455</v>
+        <v>1.559284570754986</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.600283420583866</v>
+        <v>-9.501381801471576</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.655112535797286</v>
+        <v>-0.6155518881523698</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.772868308369861</v>
+        <v>-2.700564969593976</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.521636271728092</v>
+        <v>1.565018274993622</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.353296170390914</v>
+        <v>-9.254394551278624</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.5660548981139706</v>
+        <v>-0.5264942504690544</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.453577719401024</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.660091359449998</v>
+        <v>1.703473362715528</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.089459303186844</v>
+        <v>-8.990557684074554</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4704036325452501</v>
+        <v>-0.4308429849003343</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.453577719401024</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.65020787813709</v>
+        <v>1.693589881402621</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.822217502318447</v>
+        <v>-8.723315883206157</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3653414726972648</v>
+        <v>-0.3257808250523486</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.525881058176909</v>
+        <v>-2.453577719401024</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.648373317637716</v>
+        <v>1.691755320903247</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.546408338917962</v>
+        <v>-8.447506719805672</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2553181223105319</v>
+        <v>-0.2157574746656157</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.436861749898175</v>
+        <v>-2.364558411122291</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.701484587631496</v>
+        <v>1.744866590897026</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.277340751150982</v>
+        <v>-8.178439132038692</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1470225810582462</v>
+        <v>-0.10746193341333</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.167794162131196</v>
+        <v>-2.095490823355311</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.863593646437177</v>
+        <v>1.906975649702707</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.013280812828185</v>
+        <v>-7.914379193715896</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05465892189087951</v>
+        <v>-0.01509827424596377</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.9037342238084</v>
+        <v>-1.831430885032515</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.008769293269102</v>
+        <v>2.052151296534633</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.306201189323347</v>
+        <v>-7.207299570211058</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2253858938507549</v>
+        <v>0.2649465414956707</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.9037342238084</v>
+        <v>-1.831430885032515</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.005982259608801</v>
+        <v>2.049364262874332</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.056560159337395</v>
+        <v>-6.957658540225106</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.3255859297329771</v>
+        <v>0.3651465773778928</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.654093193822448</v>
+        <v>-1.581789855046563</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.156110501488214</v>
+        <v>2.199492504753745</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.80201825999632</v>
+        <v>-6.70311664088403</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.4267695106901641</v>
+        <v>0.4663301583350798</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.399551294481372</v>
+        <v>-1.327247955705488</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.308202462313616</v>
+        <v>2.351584465579147</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.568537037766721</v>
+        <v>-6.469635418654431</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.5280864284198556</v>
+        <v>0.5676470760647718</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.166070072251774</v>
+        <v>-1.093766733475889</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.456215624489228</v>
+        <v>2.499597627754758</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.388828507622849</v>
+        <v>-6.289926888510559</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.5970776301644456</v>
+        <v>0.6366382778093618</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.108898568089078</v>
+        <v>-1.036595229313193</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.487626316673886</v>
+        <v>2.531008319939417</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.256553033991962</v>
+        <v>-6.157651414879672</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.6453553063638271</v>
+        <v>0.6849159540087433</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9766230944581911</v>
+        <v>-0.9043197556823066</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.562359087599445</v>
+        <v>2.605741090864976</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.06595335931881</v>
+        <v>-5.96705174020652</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.724410236920725</v>
+        <v>0.7639708845656412</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7860234197850382</v>
+        <v>-0.7137200810091537</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.679533953090973</v>
+        <v>2.722915956356504</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.816953560635229</v>
+        <v>-5.718051941522939</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.8369164976178163</v>
+        <v>0.876477145262732</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7860234197850382</v>
+        <v>-0.7137200810091537</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.692440294314632</v>
+        <v>2.735822297580163</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.922543550408333</v>
+        <v>-5.823641931296043</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.6667045721093556</v>
+        <v>0.7062652197542718</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8916134095581425</v>
+        <v>-0.819310070782258</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.501110370851551</v>
+        <v>2.544492374117082</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.94127845252693</v>
+        <v>-5.84237683341464</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.7077549531390033</v>
+        <v>0.7473156007839195</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8916134095581425</v>
+        <v>-0.819310070782258</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.549654712728637</v>
+        <v>2.593036715994168</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.664540277856117</v>
+        <v>-5.565638658743827</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.8218292349933232</v>
+        <v>0.8613898826382389</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7097967484482167</v>
+        <v>-0.6374934096723323</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.662123721380588</v>
+        <v>2.705505724646118</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.537647871421047</v>
+        <v>-5.438746252308757</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.8638722113138728</v>
+        <v>0.903432858958789</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5106010032372623</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.729545178988151</v>
+        <v>2.772927182253682</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.350060363511121</v>
+        <v>-5.251158744398831</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.9319466023827503</v>
+        <v>0.9715072500276665</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5106010032372623</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.722584566893058</v>
+        <v>2.765966570158589</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.107911970057263</v>
+        <v>-5.009010350944973</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.043268314145437</v>
+        <v>1.082828961790353</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5106010032372623</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.737046921274201</v>
+        <v>2.780428924539732</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.044682598288914</v>
+        <v>-4.945780979176624</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.063092183311971</v>
+        <v>1.102652830956887</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5829043420131468</v>
+        <v>-0.5106010032372623</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.731579041733396</v>
+        <v>2.774961044998927</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.858194905911908</v>
+        <v>-4.759293286799618</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.13518535427335</v>
+        <v>1.174746001918266</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3964166496361405</v>
+        <v>-0.3241133108602561</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.840969751170177</v>
+        <v>2.884351754435707</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.837045707008465</v>
+        <v>-4.738144087896175</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.151346012072053</v>
+        <v>1.190906659716969</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3752674507326972</v>
+        <v>-0.3029641119568127</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.861360248749568</v>
+        <v>2.904742252015099</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.593280265025021</v>
+        <v>-4.494378645912731</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.244632897212482</v>
+        <v>1.284193544857398</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3752674507326972</v>
+        <v>-0.3029641119568127</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.857140957096619</v>
+        <v>2.90052296036215</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.32925219783176</v>
+        <v>-4.23035057871947</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.352368438009802</v>
+        <v>1.391929085654718</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.1010987131408592</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.980384510306207</v>
+        <v>3.023766513571738</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.079401803882686</v>
+        <v>-3.980500184770396</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.445050670573134</v>
+        <v>1.48461131821805</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.1010987131408592</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.97312658528991</v>
+        <v>3.01650858855544</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.775834314878707</v>
+        <v>-3.676932695766417</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.570076789695374</v>
+        <v>1.60963743734029</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1734020519167436</v>
+        <v>-0.1010987131408592</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.976725708810558</v>
+        <v>3.020107712076089</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.702354406026693</v>
+        <v>-3.603452786914403</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.612796259290733</v>
+        <v>1.652356906935649</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.09992214306472924</v>
+        <v>-0.02761880428884478</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.034141160176321</v>
+        <v>3.077523163441851</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.47732140635787</v>
+        <v>-3.37841978724558</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.70182993677456</v>
+        <v>1.741390584419475</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1251108566040936</v>
+        <v>0.1974141953799781</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.168181437593911</v>
+        <v>3.211563440859442</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.427626402812001</v>
+        <v>3.804262151513527</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.273035499452891</v>
+        <v>-3.264248486833932</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.788239100590868</v>
+        <v>1.791753905638452</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3293967635090722</v>
+        <v>0.3115854957916264</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.295447782791216</v>
+        <v>3.284761022160748</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240404.xlsx
+++ b/tame_output/ON/bt/strategyON_20240404.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.0%</t>
+          <t>112.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.4%</t>
+          <t>130.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-624.4%</t>
+          <t>-634.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.1%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>500.9%</t>
+          <t>495.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-488.0%</t>
+          <t>-511.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-250.2%</t>
+          <t>-254.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>522.5%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-197.0%</t>
+          <t>-206.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-299.4%</t>
+          <t>-306.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-162.6%</t>
+          <t>-158.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-192.8%</t>
+          <t>-213.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-180.0%</t>
+          <t>-184.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-117.5%</t>
+          <t>-130.0%</t>
         </is>
       </c>
     </row>
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.302155344464648</v>
+        <v>-4.401056963576938</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.402852971931177</v>
+        <v>1.363292324286261</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.6713044055212015</v>
+        <v>-0.7436077442970859</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.721288890718063</v>
+        <v>2.677906887452532</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310987</v>
+        <v>3.284619513310986</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.628587873332392</v>
+        <v>-4.727489492444682</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.26056473538617</v>
+        <v>1.221004087741254</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.7537726560283498</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.660092715415865</v>
+        <v>2.616710712150335</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.630152024442695</v>
+        <v>-4.729053643554985</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.258519666598014</v>
+        <v>1.218959018953099</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.7537726560283498</v>
+        <v>-0.826075994804234</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.65867330707183</v>
+        <v>2.6152913038063</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309429</v>
+        <v>3.311086391309428</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.993778269343008</v>
+        <v>-5.092679888455298</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.11955672887213</v>
+        <v>1.079996081227215</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8519942928954756</v>
+        <v>-0.9242976316713598</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.606227885185796</v>
+        <v>2.562845881920266</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.30471571697091</v>
+        <v>3.304715716970909</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.99135120481429</v>
+        <v>-5.09025282392658</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.119782069689449</v>
+        <v>1.080221422044533</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.8523270747026273</v>
+        <v>-0.9246304134785115</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.605282731107336</v>
+        <v>2.561900727841806</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330527</v>
+        <v>3.300815818330526</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.399939981994968</v>
+        <v>-5.498841601107259</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9551081028319368</v>
+        <v>0.9155474551870211</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.260915851883306</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.358891008813688</v>
+        <v>2.315509005548158</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191742</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.812922466136062</v>
+        <v>-5.911824085248353</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7851005416469601</v>
+        <v>0.7455398940020439</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.260915851883306</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.354076441285149</v>
+        <v>2.310694438019619</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108644</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.229314340423059</v>
+        <v>-6.32821595953535</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6165378425410384</v>
+        <v>0.5769771948961222</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.260915851883306</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.352070491894026</v>
+        <v>2.308688488628496</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.605991350952904</v>
+        <v>-6.704892970065194</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4761257289977796</v>
+        <v>0.4365650813528634</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.260915851883306</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.362329182562705</v>
+        <v>2.318947179297175</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.619706215278015</v>
+        <v>-6.718607834390306</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4667393484134301</v>
+        <v>0.4271787007685144</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.260915851883306</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.358428747708401</v>
+        <v>2.31504674444287</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199291</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.932531014522994</v>
+        <v>-7.031432633635285</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3400143487704392</v>
+        <v>0.3004537011255235</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.260915851883306</v>
+        <v>-1.33321919065919</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.356833667763402</v>
+        <v>2.313451664497871</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.937344052988331</v>
+        <v>-7.036245672100622</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3418681093135127</v>
+        <v>0.3023074616685966</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.262462486586092</v>
+        <v>-1.334765825361976</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.359684662870938</v>
+        <v>2.316302659605408</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.370693161098568</v>
+        <v>-7.469594780210858</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1645021615350153</v>
+        <v>0.1249415138900991</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.262462486586092</v>
+        <v>-1.334765825361976</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.355658358336535</v>
+        <v>2.312276355071005</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.753694549841199</v>
+        <v>-7.85259616895349</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.01119950471637843</v>
+        <v>-0.02836114292853731</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.262462486586092</v>
+        <v>-1.334765825361976</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.355556257014951</v>
+        <v>2.312174253749421</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317622</v>
+        <v>3.447750501317621</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.128679876012477</v>
+        <v>-8.227581495124767</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1362231097807021</v>
+        <v>-0.1757837574256182</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.637447812757369</v>
+        <v>-1.709751151533253</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.133136577283615</v>
+        <v>2.089754574018084</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737176</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.488210198516478</v>
+        <v>-8.587111817628768</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2746849354842524</v>
+        <v>-0.3142455831291686</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.637447812757369</v>
+        <v>-1.709751151533253</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.138486880581665</v>
+        <v>2.095104877316134</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341319</v>
+        <v>3.503170282341318</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.814610227181491</v>
+        <v>-8.913511846293781</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3973289269930804</v>
+        <v>-0.4368895746379962</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.963847841422382</v>
+        <v>-2.036151180198266</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.950562883339835</v>
+        <v>1.907180880074304</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.808134080387932</v>
+        <v>-8.907035699500222</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3916967176538875</v>
+        <v>-0.4312573652988037</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.957371694628822</v>
+        <v>-2.029675033404706</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.95749032203774</v>
+        <v>1.914108318772209</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.804443155431521</v>
+        <v>-8.903344774543811</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3902203476713235</v>
+        <v>-0.4297809953162393</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.957371694628822</v>
+        <v>-2.029675033404706</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.95749032203774</v>
+        <v>1.914108318772209</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.008701330761385</v>
+        <v>-9.107602949873675</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4664104206846265</v>
+        <v>-0.5059710683295426</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.085010639242811</v>
+        <v>-2.157313978018695</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.886420152387988</v>
+        <v>1.843038149122458</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.16934035724975</v>
+        <v>-9.26824197636204</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5261834767955365</v>
+        <v>-0.5657441244404526</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.199744112245207</v>
+        <v>-2.272047451021091</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.822062623070987</v>
+        <v>1.778680619805457</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.095870525582301</v>
+        <v>-9.194772144694591</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4814238426351358</v>
+        <v>-0.5209844902800516</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.126274280577758</v>
+        <v>-2.198577619353642</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.881516223564877</v>
+        <v>1.838134220299347</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.270994942968844</v>
+        <v>-9.369896562081134</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5369183888422362</v>
+        <v>-0.5764790364871524</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.301398697964302</v>
+        <v>-2.373702036740186</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.790996793880468</v>
+        <v>1.747614790614937</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.505447036983334</v>
+        <v>-9.604348656095624</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.6379183913496282</v>
+        <v>-0.677479038994544</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.301398697964302</v>
+        <v>-2.373702036740186</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.783777628978872</v>
+        <v>1.740395625713341</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.793250881520573</v>
+        <v>-9.892152500632863</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.7597121199385</v>
+        <v>-0.7992727675834157</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.58920254250154</v>
+        <v>-2.661505881277424</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.604423131482553</v>
+        <v>1.561041128217022</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.0230753286844</v>
+        <v>-10.12197694779669</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8505261089654734</v>
+        <v>-0.8900867566103896</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.751850079571701</v>
+        <v>-2.824153418347585</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.507950399079013</v>
+        <v>1.464568395813482</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.25510424842066</v>
+        <v>-10.35400586753295</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9406439482308637</v>
+        <v>-0.9802045958757799</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.813862776760124</v>
+        <v>-2.886166115536008</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.473436509395073</v>
+        <v>1.430054506129543</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.20308873445185</v>
+        <v>-10.30199035356414</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9158474069569378</v>
+        <v>-0.9554080546018531</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.813862776760124</v>
+        <v>-2.886166115536008</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.477426845081474</v>
+        <v>1.434044841815944</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.34476057617597</v>
+        <v>-10.44366219528826</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.9739913705453276</v>
+        <v>-1.013552018190243</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.813862776760124</v>
+        <v>-2.886166115536008</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.475951618182733</v>
+        <v>1.432569614917202</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.44366731663524</v>
+        <v>-10.54256893574753</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.9985006565641652</v>
+        <v>-1.038061304209081</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.912769517219399</v>
+        <v>-2.985072855995284</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.43166098407204</v>
+        <v>1.388278980806509</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.24451520939814</v>
+        <v>-10.34341682851043</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9318909473160084</v>
+        <v>-0.9714515949609246</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.747446991269586</v>
+        <v>-2.81975033004547</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.517803365995245</v>
+        <v>1.474421362729714</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.01867005667873</v>
+        <v>-10.11757167579102</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8319738131920356</v>
+        <v>-0.8715344608369517</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.705520315682422</v>
+        <v>-2.777823654458307</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.552538444383752</v>
+        <v>1.509156441118221</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282103</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.732395244356038</v>
+        <v>-9.831296863468328</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7163247437068989</v>
+        <v>-0.7558853913518151</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.705520315682422</v>
+        <v>-2.777823654458307</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.55367758893981</v>
+        <v>1.51029558567428</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.785290532400325</v>
+        <v>-9.884192151512615</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.734849084762506</v>
+        <v>-0.7744097324074222</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.700564969593976</v>
+        <v>-2.772868308369861</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.559284570754986</v>
+        <v>1.515902567489455</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.501381801471576</v>
+        <v>-9.600283420583866</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6155518881523698</v>
+        <v>-0.655112535797286</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.700564969593976</v>
+        <v>-2.772868308369861</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.565018274993622</v>
+        <v>1.521636271728092</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425331</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.254394551278624</v>
+        <v>-9.58960928302751</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.5264942504690544</v>
+        <v>-0.6605801431686089</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.453577719401024</v>
+        <v>-2.762194170813505</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.703473362715528</v>
+        <v>1.51830349186804</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702416</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.990557684074554</v>
+        <v>-9.32577241582344</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4308429849003343</v>
+        <v>-0.5649288775998884</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.453577719401024</v>
+        <v>-2.762194170813505</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.693589881402621</v>
+        <v>1.508420010555132</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906231</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.723315883206157</v>
+        <v>-9.058530614955043</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3257808250523486</v>
+        <v>-0.4598667177519031</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.453577719401024</v>
+        <v>-2.762194170813505</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.691755320903247</v>
+        <v>1.506585450055759</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781951</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.447506719805672</v>
+        <v>-8.782721451554558</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2157574746656157</v>
+        <v>-0.3498433673651702</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.364558411122291</v>
+        <v>-2.673174862534772</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.744866590897026</v>
+        <v>1.559696720049538</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.178439132038692</v>
+        <v>-8.513653863787578</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.10746193341333</v>
+        <v>-0.2415478261128845</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.095490823355311</v>
+        <v>-2.404107274767792</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.906975649702707</v>
+        <v>1.721805778855219</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.914379193715896</v>
+        <v>-8.249593925464781</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.01509827424596377</v>
+        <v>-0.1491841669455178</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.831430885032515</v>
+        <v>-2.140047336444996</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.052151296534633</v>
+        <v>1.866981425687145</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.207299570211058</v>
+        <v>-7.542514301959943</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2649465414956707</v>
+        <v>0.1308606487961166</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.831430885032515</v>
+        <v>-2.140047336444996</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.049364262874332</v>
+        <v>1.864194392026844</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-6.957658540225106</v>
+        <v>-7.292873271973991</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.3651465773778928</v>
+        <v>0.2310606846783387</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.581789855046563</v>
+        <v>-1.890406306459044</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.199492504753745</v>
+        <v>2.014322633906256</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.70311664088403</v>
+        <v>-7.038331372632916</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.4663301583350798</v>
+        <v>0.3322442656355253</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.327247955705488</v>
+        <v>-1.635864407117969</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.351584465579147</v>
+        <v>2.166414594731658</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.469635418654431</v>
+        <v>-6.804850150403317</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.5676470760647718</v>
+        <v>0.4335611833652173</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.093766733475889</v>
+        <v>-1.40238318488837</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.499597627754758</v>
+        <v>2.31442775690727</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.289926888510559</v>
+        <v>-6.625141620259445</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.6366382778093618</v>
+        <v>0.5025523851098073</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.036595229313193</v>
+        <v>-1.345211680725674</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.531008319939417</v>
+        <v>2.345838449091929</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.157651414879672</v>
+        <v>-6.492866146628558</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.6849159540087433</v>
+        <v>0.5508300613091888</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9043197556823066</v>
+        <v>-1.212936207094787</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.605741090864976</v>
+        <v>2.420571220017488</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-5.96705174020652</v>
+        <v>-6.302266471955406</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.7639708845656412</v>
+        <v>0.6298849918660867</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7137200810091537</v>
+        <v>-1.022336532421634</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.722915956356504</v>
+        <v>2.537746085509016</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.718051941522939</v>
+        <v>-6.053266673271825</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.876477145262732</v>
+        <v>0.7423912525631775</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7137200810091537</v>
+        <v>-1.022336532421634</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.735822297580163</v>
+        <v>2.550652426732674</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.823641931296043</v>
+        <v>-6.158856663044929</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.7062652197542718</v>
+        <v>0.5721793270547173</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.819310070782258</v>
+        <v>-1.127926522194739</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.544492374117082</v>
+        <v>2.359322503269593</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.84237683341464</v>
+        <v>-6.177591565163526</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.7473156007839195</v>
+        <v>0.6132297080843649</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.819310070782258</v>
+        <v>-1.127926522194739</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.593036715994168</v>
+        <v>2.40786684514668</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.565638658743827</v>
+        <v>-5.900853390492713</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.8613898826382389</v>
+        <v>0.7273039899386848</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6374934096723323</v>
+        <v>-0.946109861084813</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.705505724646118</v>
+        <v>2.52033585379863</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.438746252308757</v>
+        <v>-5.773960984057643</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.903432858958789</v>
+        <v>0.7693469662592345</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5106010032372623</v>
+        <v>-0.819217454649743</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.772927182253682</v>
+        <v>2.587757311406194</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.251158744398831</v>
+        <v>-5.586373476147717</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.9715072500276665</v>
+        <v>0.837421357328112</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5106010032372623</v>
+        <v>-0.819217454649743</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.765966570158589</v>
+        <v>2.5807966993111</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.009010350944973</v>
+        <v>-5.344225082693859</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.082828961790353</v>
+        <v>0.9487430690907983</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5106010032372623</v>
+        <v>-0.819217454649743</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.780428924539732</v>
+        <v>2.595259053692244</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-4.945780979176624</v>
+        <v>-5.28099571092551</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.102652830956887</v>
+        <v>0.9685669382573328</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5106010032372623</v>
+        <v>-0.819217454649743</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.774961044998927</v>
+        <v>2.589791174151439</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.759293286799618</v>
+        <v>-5.094508018548504</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.174746001918266</v>
+        <v>1.040660109218712</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.3241133108602561</v>
+        <v>-0.6327297622727368</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.884351754435707</v>
+        <v>2.699181883588219</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.738144087896175</v>
+        <v>-5.073358819645061</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.190906659716969</v>
+        <v>1.056820767017415</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3029641119568127</v>
+        <v>-0.6115805633692935</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.904742252015099</v>
+        <v>2.719572381167611</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.494378645912731</v>
+        <v>-4.829593377661617</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.284193544857398</v>
+        <v>1.150107652157843</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3029641119568127</v>
+        <v>-0.6115805633692935</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.90052296036215</v>
+        <v>2.715353089514661</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.23035057871947</v>
+        <v>-4.565565310468356</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.391929085654718</v>
+        <v>1.257843192955163</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1010987131408592</v>
+        <v>-0.4097151645533399</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.023766513571738</v>
+        <v>2.83859664272425</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-3.980500184770396</v>
+        <v>-4.315714916519282</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.48461131821805</v>
+        <v>1.350525425518496</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1010987131408592</v>
+        <v>-0.4097151645533399</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.01650858855544</v>
+        <v>2.831338717707952</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.676932695766417</v>
+        <v>-4.012147427515303</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.60963743734029</v>
+        <v>1.475551544640736</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1010987131408592</v>
+        <v>-0.4097151645533399</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.020107712076089</v>
+        <v>2.834937841228601</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.603452786914403</v>
+        <v>-3.938667518663288</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.652356906935649</v>
+        <v>1.518271014236095</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.02761880428884478</v>
+        <v>-0.3362352557013255</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.077523163441851</v>
+        <v>2.892353292594363</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.37841978724558</v>
+        <v>-3.713634518994466</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.741390584419475</v>
+        <v>1.607304691719921</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1974141953799781</v>
+        <v>-0.1112022560325027</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.211563440859442</v>
+        <v>3.026393570011953</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.804262151513527</v>
+        <v>3.422166143296788</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.264248486833932</v>
+        <v>-3.499000141358059</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.791753905638452</v>
+        <v>1.697853243828801</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3115854957916264</v>
+        <v>0.1034321216039041</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.284761022160748</v>
+        <v>3.159868997648115</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240404.xlsx
+++ b/tame_output/ON/bt/strategyON_20240404.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,75 +801,75 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-29.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.4%</t>
+          <t>112.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.6%</t>
+          <t>130.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>495.6%</t>
+          <t>495.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-03</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,47 +1461,47 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-26.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-130.0%</t>
+          <t>-165.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1923"/>
+  <dimension ref="A1:G1924"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207818</v>
+        <v>3.305316798207817</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006538</v>
+        <v>3.305849539006537</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191741</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108643</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857435442533</v>
+        <v>3.728574354425329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702415</v>
+        <v>3.747699084702414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631350390623</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487775</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.422166143296788</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
@@ -45790,6 +45790,29 @@
       </c>
       <c r="G1923" t="n">
         <v>3.159868997648115</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="B1924" t="n">
+        <v>3.419004734100104</v>
+      </c>
+      <c r="C1924" t="n">
+        <v>2.817589465250079</v>
+      </c>
+      <c r="D1924" t="n">
+        <v>-3.499000141358059</v>
+      </c>
+      <c r="E1924" t="n">
+        <v>1.697853243828801</v>
+      </c>
+      <c r="F1924" t="n">
+        <v>0.1034321216039041</v>
+      </c>
+      <c r="G1924" t="n">
+        <v>2.810653262236447</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240404.xlsx
+++ b/tame_output/ON/bt/strategyON_20240404.xlsx
@@ -45800,7 +45800,7 @@
         <v>3.419004734100104</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.817589465250079</v>
+        <v>2.817589465250078</v>
       </c>
       <c r="D1924" t="n">
         <v>-3.499000141358059</v>
@@ -45812,7 +45812,7 @@
         <v>0.1034321216039041</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.810653262236447</v>
+        <v>2.810653262236446</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240404.xlsx
+++ b/tame_output/ON/bt/strategyON_20240404.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,75 +801,75 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.9%</t>
+          <t>-3.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.3%</t>
+          <t>112.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.5%</t>
+          <t>130.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-634.3%</t>
+          <t>-635.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>495.5%</t>
+          <t>499.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-511.5%</t>
+          <t>-513.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-254.1%</t>
+          <t>-254.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-206.4%</t>
+          <t>-207.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-306.6%</t>
+          <t>-305.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.9%</t>
+          <t>-159.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.6%</t>
+          <t>-212.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-184.4%</t>
+          <t>-183.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.0%</t>
+          <t>-138.6%</t>
         </is>
       </c>
     </row>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207817</v>
+        <v>3.305316798207818</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.727489492444682</v>
+        <v>-4.742474372481648</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.221004087741254</v>
+        <v>1.215010135726468</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.8098202525745194</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.616710712150335</v>
+        <v>2.626464157488163</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.729053643554985</v>
+        <v>-4.744038523591951</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.218959018953099</v>
+        <v>1.212965066938312</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.826075994804234</v>
+        <v>-0.8098202525745194</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.6152913038063</v>
+        <v>2.625044749144128</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.092679888455298</v>
+        <v>-5.107664768492264</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.079996081227215</v>
+        <v>1.074002129212428</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9242976316713598</v>
+        <v>-0.9080418894416452</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.562845881920266</v>
+        <v>2.572599327258094</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.09025282392658</v>
+        <v>-5.105237703963546</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.080221422044533</v>
+        <v>1.074227470029747</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9246304134785115</v>
+        <v>-0.9083746712487968</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.561900727841806</v>
+        <v>2.571654173179635</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.498841601107259</v>
+        <v>-5.513826481144225</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9155474551870211</v>
+        <v>0.9095535031722344</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.316963448429475</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.315509005548158</v>
+        <v>2.325262450885987</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.911824085248353</v>
+        <v>-5.926808965285319</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7455398940020439</v>
+        <v>0.7395459419872576</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.316963448429475</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.310694438019619</v>
+        <v>2.320447883357447</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.32821595953535</v>
+        <v>-6.343200839572316</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5769771948961222</v>
+        <v>0.570983242881336</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.316963448429475</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.308688488628496</v>
+        <v>2.318441933966325</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.704892970065194</v>
+        <v>-6.719877850102161</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4365650813528634</v>
+        <v>0.4305711293380772</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.316963448429475</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.318947179297175</v>
+        <v>2.328700624635004</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.718607834390306</v>
+        <v>-6.733592714427272</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4271787007685144</v>
+        <v>0.4211847487537277</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.316963448429475</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.31504674444287</v>
+        <v>2.324800189780699</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.031432633635285</v>
+        <v>-7.046417513672251</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3004537011255235</v>
+        <v>0.2944597491107368</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.33321919065919</v>
+        <v>-1.316963448429475</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.313451664497871</v>
+        <v>2.3232051098357</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.036245672100622</v>
+        <v>-7.051230552137588</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3023074616685966</v>
+        <v>0.2963135096538103</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.318510083132261</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.316302659605408</v>
+        <v>2.326056104943237</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.469594780210858</v>
+        <v>-7.484579660247825</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1249415138900991</v>
+        <v>0.1189475618753129</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.318510083132261</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.312276355071005</v>
+        <v>2.322029800408834</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.85259616895349</v>
+        <v>-7.867581048990456</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.02836114292853731</v>
+        <v>-0.034355094943324</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.334765825361976</v>
+        <v>-1.318510083132261</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.312174253749421</v>
+        <v>2.321927699087249</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.227581495124767</v>
+        <v>-8.242566375161733</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1757837574256182</v>
+        <v>-0.1817777094404045</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.693495409303538</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.089754574018084</v>
+        <v>2.099508019355913</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.587111817628768</v>
+        <v>-8.602096697665734</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3142455831291686</v>
+        <v>-0.3202395351439549</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.709751151533253</v>
+        <v>-1.693495409303538</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.095104877316134</v>
+        <v>2.104858322653963</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.913511846293781</v>
+        <v>-8.928496726330748</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.4368895746379962</v>
+        <v>-0.4428835266527829</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.036151180198266</v>
+        <v>-2.019895437968551</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.907180880074304</v>
+        <v>1.916934325412133</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.907035699500222</v>
+        <v>-8.922020579537188</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4312573652988037</v>
+        <v>-0.4372513173135899</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.029675033404706</v>
+        <v>-2.013419291174992</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.914108318772209</v>
+        <v>1.923861764110038</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.903344774543811</v>
+        <v>-8.918329654580777</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4297809953162393</v>
+        <v>-0.435774947331026</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.029675033404706</v>
+        <v>-2.013419291174992</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.914108318772209</v>
+        <v>1.923861764110038</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.107602949873675</v>
+        <v>-9.122587829910641</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.5059710683295426</v>
+        <v>-0.5119650203443289</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.157313978018695</v>
+        <v>-2.14105823578898</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.843038149122458</v>
+        <v>1.852791594460287</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.26824197636204</v>
+        <v>-9.283226856399006</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5657441244404526</v>
+        <v>-0.5717380764552389</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.272047451021091</v>
+        <v>-2.255791708791376</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.778680619805457</v>
+        <v>1.788434065143286</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.194772144694591</v>
+        <v>-9.209757024731557</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5209844902800516</v>
+        <v>-0.5269784422948383</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.198577619353642</v>
+        <v>-2.182321877123928</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.838134220299347</v>
+        <v>1.847887665637176</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.369896562081134</v>
+        <v>-9.3848814421181</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5764790364871524</v>
+        <v>-0.5824729885019386</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.357446294510471</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.747614790614937</v>
+        <v>1.757368235952766</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.604348656095624</v>
+        <v>-9.61933353613259</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.677479038994544</v>
+        <v>-0.6834729910093307</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.373702036740186</v>
+        <v>-2.357446294510471</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.740395625713341</v>
+        <v>1.75014907105117</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.892152500632863</v>
+        <v>-9.907137380669829</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.7992727675834157</v>
+        <v>-0.8052667195982024</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.661505881277424</v>
+        <v>-2.64525013904771</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.561041128217022</v>
+        <v>1.570794573554851</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.12197694779669</v>
+        <v>-10.13696182783365</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8900867566103896</v>
+        <v>-0.8960807086251759</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.824153418347585</v>
+        <v>-2.80789767611787</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.464568395813482</v>
+        <v>1.474321841151311</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.35400586753295</v>
+        <v>-10.36899074756992</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9802045958757799</v>
+        <v>-0.9861985478905662</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.869910373306293</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.430054506129543</v>
+        <v>1.439807951467372</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.30199035356414</v>
+        <v>-10.3169752336011</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9554080546018531</v>
+        <v>-0.9614020066166402</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.869910373306293</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.434044841815944</v>
+        <v>1.443798287153773</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.44366219528826</v>
+        <v>-10.45864707532522</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.013552018190243</v>
+        <v>-1.01954597020503</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.886166115536008</v>
+        <v>-2.869910373306293</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.432569614917202</v>
+        <v>1.442323060255031</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.54256893574753</v>
+        <v>-10.5575538157845</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.038061304209081</v>
+        <v>-1.044055256223868</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.985072855995284</v>
+        <v>-2.968817113765569</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.388278980806509</v>
+        <v>1.398032426144338</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.34341682851043</v>
+        <v>-10.3584017085474</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9714515949609246</v>
+        <v>-0.9774455469757108</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81975033004547</v>
+        <v>-2.803494587815755</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.474421362729714</v>
+        <v>1.484174808067543</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.11757167579102</v>
+        <v>-10.13255655582799</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.8715344608369517</v>
+        <v>-0.877528412851738</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.761567912228592</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.509156441118221</v>
+        <v>1.51890988645605</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.831296863468328</v>
+        <v>-9.846281743505294</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7558853913518151</v>
+        <v>-0.7618793433666013</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.777823654458307</v>
+        <v>-2.761567912228592</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.51029558567428</v>
+        <v>1.520049031012109</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.884192151512615</v>
+        <v>-9.899177031549581</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7744097324074222</v>
+        <v>-0.7804036844222084</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.772868308369861</v>
+        <v>-2.756612566140145</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.515902567489455</v>
+        <v>1.525656012827284</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.600283420583866</v>
+        <v>-9.615268300620832</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.655112535797286</v>
+        <v>-0.6611064878120723</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.772868308369861</v>
+        <v>-2.756612566140145</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.521636271728092</v>
+        <v>1.531389717065921</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.58960928302751</v>
+        <v>-9.604594163064476</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6605801431686089</v>
+        <v>-0.6665740951833952</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.762194170813505</v>
+        <v>-2.74593842858379</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.51830349186804</v>
+        <v>1.528056937205869</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.32577241582344</v>
+        <v>-9.340757295860406</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5649288775998884</v>
+        <v>-0.5709228296146751</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.762194170813505</v>
+        <v>-2.74593842858379</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.508420010555132</v>
+        <v>1.518173455892961</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.058530614955043</v>
+        <v>-9.073515494992009</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4598667177519031</v>
+        <v>-0.4658606697666898</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.762194170813505</v>
+        <v>-2.74593842858379</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.506585450055759</v>
+        <v>1.516338895393587</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.782721451554558</v>
+        <v>-8.797706331591524</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3498433673651702</v>
+        <v>-0.3558373193799564</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.673174862534772</v>
+        <v>-2.656919120305056</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.559696720049538</v>
+        <v>1.569450165387367</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.513653863787578</v>
+        <v>-8.528638743824544</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2415478261128845</v>
+        <v>-0.2475417781276712</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.404107274767792</v>
+        <v>-2.387851532538077</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.721805778855219</v>
+        <v>1.731559224193048</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.249593925464781</v>
+        <v>-8.264578805501747</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1491841669455178</v>
+        <v>-0.1551781189603045</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.140047336444996</v>
+        <v>-2.123791594215281</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.866981425687145</v>
+        <v>1.876734871024974</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.542514301959943</v>
+        <v>-7.557499181996909</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1308606487961166</v>
+        <v>0.1248666967813299</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.140047336444996</v>
+        <v>-2.123791594215281</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.864194392026844</v>
+        <v>1.873947837364673</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.292873271973991</v>
+        <v>-7.307858152010957</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2310606846783387</v>
+        <v>0.225066732663552</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.890406306459044</v>
+        <v>-1.874150564229329</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.014322633906256</v>
+        <v>2.024076079244085</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.038331372632916</v>
+        <v>-7.053316252669882</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3322442656355253</v>
+        <v>0.3262503136207391</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.635864407117969</v>
+        <v>-1.619608664888254</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.166414594731658</v>
+        <v>2.176168040069487</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.804850150403317</v>
+        <v>-6.819835030440283</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4335611833652173</v>
+        <v>0.4275672313504311</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.40238318488837</v>
+        <v>-1.386127442658655</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.31442775690727</v>
+        <v>2.324181202245099</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.625141620259445</v>
+        <v>-6.640126500296411</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.5025523851098073</v>
+        <v>0.4965584330950206</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.345211680725674</v>
+        <v>-1.328955938495959</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.345838449091929</v>
+        <v>2.355591894429757</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.492866146628558</v>
+        <v>-6.507851026665525</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5508300613091888</v>
+        <v>0.5448361092944025</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.212936207094787</v>
+        <v>-1.196680464865072</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.420571220017488</v>
+        <v>2.430324665355316</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.302266471955406</v>
+        <v>-6.317251351992372</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.6298849918660867</v>
+        <v>0.6238910398513</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.022336532421634</v>
+        <v>-1.006080790191919</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.537746085509016</v>
+        <v>2.547499530846845</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.053266673271825</v>
+        <v>-6.068251553308791</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.7423912525631775</v>
+        <v>0.7363973005483913</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.022336532421634</v>
+        <v>-1.006080790191919</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.550652426732674</v>
+        <v>2.560405872070504</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.158856663044929</v>
+        <v>-6.173841543081895</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5721793270547173</v>
+        <v>0.5661853750399306</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.127926522194739</v>
+        <v>-1.111670779965024</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.359322503269593</v>
+        <v>2.369075948607422</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.177591565163526</v>
+        <v>-6.192576445200492</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.6132297080843649</v>
+        <v>0.6072357560695782</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.127926522194739</v>
+        <v>-1.111670779965024</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.40786684514668</v>
+        <v>2.417620290484509</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.900853390492713</v>
+        <v>-5.915838270529679</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.7273039899386848</v>
+        <v>0.7213100379238981</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.946109861084813</v>
+        <v>-0.9298541188550978</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.52033585379863</v>
+        <v>2.530089299136459</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.773960984057643</v>
+        <v>-5.788945864094609</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.7693469662592345</v>
+        <v>0.7633530142444482</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.819217454649743</v>
+        <v>-0.8029617124200279</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.587757311406194</v>
+        <v>2.597510756744023</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.586373476147717</v>
+        <v>-5.601358356184683</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.837421357328112</v>
+        <v>0.8314274053133257</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.819217454649743</v>
+        <v>-0.8029617124200279</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.5807966993111</v>
+        <v>2.59055014464893</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.344225082693859</v>
+        <v>-5.359209962730825</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.9487430690907983</v>
+        <v>0.9427491170760121</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.819217454649743</v>
+        <v>-0.8029617124200279</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.595259053692244</v>
+        <v>2.605012499030073</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.28099571092551</v>
+        <v>-5.295980590962476</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.9685669382573328</v>
+        <v>0.9625729862425461</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.819217454649743</v>
+        <v>-0.8029617124200279</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.589791174151439</v>
+        <v>2.599544619489268</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.094508018548504</v>
+        <v>-5.10949289858547</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.040660109218712</v>
+        <v>1.034666157203926</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.6327297622727368</v>
+        <v>-0.6164740200430217</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.699181883588219</v>
+        <v>2.708935328926048</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.073358819645061</v>
+        <v>-5.088343699682027</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.056820767017415</v>
+        <v>1.050826815002628</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6115805633692935</v>
+        <v>-0.5953248211395783</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.719572381167611</v>
+        <v>2.72932582650544</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.829593377661617</v>
+        <v>-4.844578257698583</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.150107652157843</v>
+        <v>1.144113700143057</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6115805633692935</v>
+        <v>-0.5953248211395783</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.715353089514661</v>
+        <v>2.725106534852491</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.565565310468356</v>
+        <v>-4.580550190505322</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.257843192955163</v>
+        <v>1.251849240940377</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4097151645533399</v>
+        <v>-0.3934594223236247</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.83859664272425</v>
+        <v>2.848350088062078</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.315714916519282</v>
+        <v>-4.330699796556248</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.350525425518496</v>
+        <v>1.344531473503709</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4097151645533399</v>
+        <v>-0.3934594223236247</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.831338717707952</v>
+        <v>2.841092163045781</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.012147427515303</v>
+        <v>-4.027132307552269</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.475551544640736</v>
+        <v>1.469557592625949</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4097151645533399</v>
+        <v>-0.3934594223236247</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.834937841228601</v>
+        <v>2.844691286566429</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.938667518663288</v>
+        <v>-3.953652398700255</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.518271014236095</v>
+        <v>1.512277062221309</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3362352557013255</v>
+        <v>-0.3199795134716104</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.892353292594363</v>
+        <v>2.902106737932192</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.713634518994466</v>
+        <v>-3.728619399031432</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.607304691719921</v>
+        <v>1.601310739705135</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1112022560325027</v>
+        <v>-0.09494651380278751</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.026393570011953</v>
+        <v>3.036147015349782</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.499000141358059</v>
+        <v>-3.513985021395025</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.697853243828801</v>
+        <v>1.691859291814015</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1034321216039041</v>
+        <v>0.1196878638336193</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.159868997648115</v>
+        <v>3.169622442985944</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.419004734100104</v>
+        <v>3.735720826754782</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.817589465250078</v>
+        <v>3.081384075377701</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.499000141358059</v>
+        <v>-3.513985021395025</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.697853243828801</v>
+        <v>1.691859291814015</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1034321216039041</v>
+        <v>0.1196878638336193</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.810653262236446</v>
+        <v>3.074447872364069</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240404.xlsx
+++ b/tame_output/ON/bt/strategyON_20240404.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.4%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-635.8%</t>
+          <t>-635.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-69.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.9%</t>
+          <t>500.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-513.0%</t>
+          <t>-488.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-254.7%</t>
+          <t>-254.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-207.0%</t>
+          <t>-197.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-305.0%</t>
+          <t>-304.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.1%</t>
+          <t>-161.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-212.0%</t>
+          <t>-188.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-183.4%</t>
+          <t>-183.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.742474372481648</v>
+        <v>-4.736832839622476</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.215010135726468</v>
+        <v>1.217266748870137</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8098202525745194</v>
+        <v>-0.8088168116961421</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.626464157488163</v>
+        <v>2.627066222015189</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.744038523591951</v>
+        <v>-4.738396990732779</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.212965066938312</v>
+        <v>1.215221680081981</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8098202525745194</v>
+        <v>-0.8088168116961421</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.625044749144128</v>
+        <v>2.625646813671155</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.107664768492264</v>
+        <v>-5.102023235633093</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.074002129212428</v>
+        <v>1.076258742356097</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9080418894416452</v>
+        <v>-0.9070384485632679</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.572599327258094</v>
+        <v>2.573201391785121</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.105237703963546</v>
+        <v>-5.099596171104374</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.074227470029747</v>
+        <v>1.076484083173415</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9083746712487968</v>
+        <v>-0.9073712303704196</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.571654173179635</v>
+        <v>2.572256237706661</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.513826481144225</v>
+        <v>-5.508184948285052</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9095535031722344</v>
+        <v>0.9118101163159036</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.316963448429475</v>
+        <v>-1.315960007551098</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.325262450885987</v>
+        <v>2.325864515413013</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.926808965285319</v>
+        <v>-5.921167432426146</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7395459419872576</v>
+        <v>0.7418025551309264</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.316963448429475</v>
+        <v>-1.315960007551098</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.320447883357447</v>
+        <v>2.321049947884474</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.343200839572316</v>
+        <v>-6.337559306713143</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.570983242881336</v>
+        <v>0.5732398560250047</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.316963448429475</v>
+        <v>-1.315960007551098</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.318441933966325</v>
+        <v>2.319043998493351</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.719877850102161</v>
+        <v>-6.714236317242988</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4305711293380772</v>
+        <v>0.4328277424817459</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.316963448429475</v>
+        <v>-1.315960007551098</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.328700624635004</v>
+        <v>2.32930268916203</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.733592714427272</v>
+        <v>-6.727951181568099</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4211847487537277</v>
+        <v>0.4234413618973969</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.316963448429475</v>
+        <v>-1.315960007551098</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.324800189780699</v>
+        <v>2.325402254307726</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.046417513672251</v>
+        <v>-7.040775980813079</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2944597491107368</v>
+        <v>0.296716362254406</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.316963448429475</v>
+        <v>-1.315960007551098</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.3232051098357</v>
+        <v>2.323807174362726</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.051230552137588</v>
+        <v>-7.045589019278416</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2963135096538103</v>
+        <v>0.2985701227974791</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.318510083132261</v>
+        <v>-1.317506642253884</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.326056104943237</v>
+        <v>2.326658169470263</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.484579660247825</v>
+        <v>-7.478938127388652</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1189475618753129</v>
+        <v>0.1212041750189816</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.318510083132261</v>
+        <v>-1.317506642253884</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.322029800408834</v>
+        <v>2.32263186493586</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.867581048990456</v>
+        <v>-7.861939516131283</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.034355094943324</v>
+        <v>-0.0320984817996548</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.318510083132261</v>
+        <v>-1.317506642253884</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.321927699087249</v>
+        <v>2.322529763614276</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.242566375161733</v>
+        <v>-8.23692484230256</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1817777094404045</v>
+        <v>-0.1795210962967357</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.693495409303538</v>
+        <v>-1.692491968425161</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.099508019355913</v>
+        <v>2.10011008388294</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.602096697665734</v>
+        <v>-8.596455164806562</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3202395351439549</v>
+        <v>-0.3179829220002861</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.693495409303538</v>
+        <v>-1.692491968425161</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.104858322653963</v>
+        <v>2.10546038718099</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.928496726330748</v>
+        <v>-8.922855193471575</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.4428835266527829</v>
+        <v>-0.4406269135091136</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.019895437968551</v>
+        <v>-2.018891997090174</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.916934325412133</v>
+        <v>1.917536389939159</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.922020579537188</v>
+        <v>-8.916379046678015</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4372513173135899</v>
+        <v>-0.4349947041699211</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.013419291174992</v>
+        <v>-2.012415850296614</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.923861764110038</v>
+        <v>1.924463828637064</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.918329654580777</v>
+        <v>-8.912688121721605</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.435774947331026</v>
+        <v>-0.4335183341873567</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.013419291174992</v>
+        <v>-2.012415850296614</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.923861764110038</v>
+        <v>1.924463828637064</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.122587829910641</v>
+        <v>-9.116946297051468</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.5119650203443289</v>
+        <v>-0.5097084072006597</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.14105823578898</v>
+        <v>-2.140054794910603</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.852791594460287</v>
+        <v>1.853393658987313</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.283226856399006</v>
+        <v>-9.277585323539833</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5717380764552389</v>
+        <v>-0.5694814633115697</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.255791708791376</v>
+        <v>-2.254788267912999</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.788434065143286</v>
+        <v>1.789036129670312</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.209757024731557</v>
+        <v>-9.204115491872384</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5269784422948383</v>
+        <v>-0.5247218291511691</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.182321877123928</v>
+        <v>-2.18131843624555</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.847887665637176</v>
+        <v>1.848489730164202</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.3848814421181</v>
+        <v>-9.379239909258928</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5824729885019386</v>
+        <v>-0.5802163753582699</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.357446294510471</v>
+        <v>-2.356442853632094</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.757368235952766</v>
+        <v>1.757970300479793</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.61933353613259</v>
+        <v>-9.613692003273417</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.6834729910093307</v>
+        <v>-0.6812163778656615</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.357446294510471</v>
+        <v>-2.356442853632094</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.75014907105117</v>
+        <v>1.750751135578197</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.907137380669829</v>
+        <v>-9.901495847810656</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.8052667195982024</v>
+        <v>-0.8030101064545332</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.64525013904771</v>
+        <v>-2.644246698169332</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.570794573554851</v>
+        <v>1.571396638081877</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.13696182783365</v>
+        <v>-10.13132029497448</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.8960807086251759</v>
+        <v>-0.8938240954815067</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.80789767611787</v>
+        <v>-2.806894235239493</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.474321841151311</v>
+        <v>1.474923905678337</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.36899074756992</v>
+        <v>-10.36334921471074</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.9861985478905662</v>
+        <v>-0.983941934746897</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.869910373306293</v>
+        <v>-2.868906932427916</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.439807951467372</v>
+        <v>1.440410015994398</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.3169752336011</v>
+        <v>-10.31133370074193</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9614020066166402</v>
+        <v>-0.959145393472971</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.869910373306293</v>
+        <v>-2.868906932427916</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.443798287153773</v>
+        <v>1.444400351680799</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.45864707532522</v>
+        <v>-10.45300554246605</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.01954597020503</v>
+        <v>-1.017289357061361</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.869910373306293</v>
+        <v>-2.868906932427916</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.442323060255031</v>
+        <v>1.442925124782057</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.5575538157845</v>
+        <v>-10.55191228292533</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.044055256223868</v>
+        <v>-1.041798643080198</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.968817113765569</v>
+        <v>-2.967813672887191</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.398032426144338</v>
+        <v>1.398634490671365</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.3584017085474</v>
+        <v>-10.35276017568823</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.9774455469757108</v>
+        <v>-0.9751889338320416</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.803494587815755</v>
+        <v>-2.802491146937378</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.484174808067543</v>
+        <v>1.484776872594569</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.13255655582799</v>
+        <v>-10.12691502296882</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.877528412851738</v>
+        <v>-0.8752717997080697</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.761567912228592</v>
+        <v>-2.760564471350214</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.51890988645605</v>
+        <v>1.519511950983076</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.846281743505294</v>
+        <v>-9.840640210646121</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.7618793433666013</v>
+        <v>-0.7596227302229326</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.761567912228592</v>
+        <v>-2.760564471350214</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.520049031012109</v>
+        <v>1.520651095539135</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.899177031549581</v>
+        <v>-9.893535498690408</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7804036844222084</v>
+        <v>-0.7781470712785392</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.756612566140145</v>
+        <v>-2.755609125261768</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.525656012827284</v>
+        <v>1.526258077354311</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.615268300620832</v>
+        <v>-9.609626767761659</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6611064878120723</v>
+        <v>-0.6588498746684035</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.756612566140145</v>
+        <v>-2.755609125261768</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.531389717065921</v>
+        <v>1.531991781592947</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.604594163064476</v>
+        <v>-9.362639517568708</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6665740951833952</v>
+        <v>-0.5697922369850881</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.74593842858379</v>
+        <v>-2.508621875068816</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.528056937205869</v>
+        <v>1.670446869314853</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.340757295860406</v>
+        <v>-9.098802650364638</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5709228296146751</v>
+        <v>-0.4741409714163676</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.74593842858379</v>
+        <v>-2.508621875068816</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.518173455892961</v>
+        <v>1.660563388001945</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.073515494992009</v>
+        <v>-8.83156084949624</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4658606697666898</v>
+        <v>-0.3690788115683823</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.74593842858379</v>
+        <v>-2.508621875068816</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.516338895393587</v>
+        <v>1.658728827502572</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.797706331591524</v>
+        <v>-8.555751686095755</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3558373193799564</v>
+        <v>-0.2590554611816489</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.656919120305056</v>
+        <v>-2.419602566790083</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.569450165387367</v>
+        <v>1.711840097496351</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.528638743824544</v>
+        <v>-8.286684098328776</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2475417781276712</v>
+        <v>-0.1507599199293637</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.387851532538077</v>
+        <v>-2.150534979023103</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.731559224193048</v>
+        <v>1.873949156302032</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.264578805501747</v>
+        <v>-8.022624160005979</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1551781189603045</v>
+        <v>-0.058396260761997</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.123791594215281</v>
+        <v>-1.886475040700307</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.876734871024974</v>
+        <v>2.019124803133958</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.557499181996909</v>
+        <v>-7.31554453650114</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1248666967813299</v>
+        <v>0.2216485549796374</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.123791594215281</v>
+        <v>-1.886475040700307</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.873947837364673</v>
+        <v>2.016337769473657</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.307858152010957</v>
+        <v>-7.065903506515189</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.225066732663552</v>
+        <v>0.3218485908618596</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.874150564229329</v>
+        <v>-1.636834010714356</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.024076079244085</v>
+        <v>2.166466011353069</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.053316252669882</v>
+        <v>-6.811361607174113</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3262503136207391</v>
+        <v>0.4230321718190466</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.619608664888254</v>
+        <v>-1.38229211137328</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.176168040069487</v>
+        <v>2.318557972178472</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.819835030440283</v>
+        <v>-6.577880384944515</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4275672313504311</v>
+        <v>0.5243490895487382</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.386127442658655</v>
+        <v>-1.148810889143681</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.324181202245099</v>
+        <v>2.466571134354083</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.640126500296411</v>
+        <v>-6.398171854800642</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4965584330950206</v>
+        <v>0.5933402912933281</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.328955938495959</v>
+        <v>-1.091639384980985</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.355591894429757</v>
+        <v>2.497981826538742</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.507851026665525</v>
+        <v>-6.265896381169756</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5448361092944025</v>
+        <v>0.6416179674927096</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.196680464865072</v>
+        <v>-0.9593639113500987</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.430324665355316</v>
+        <v>2.572714597464301</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.317251351992372</v>
+        <v>-6.075296706496603</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.6238910398513</v>
+        <v>0.7206728980496075</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.006080790191919</v>
+        <v>-0.7687642366769458</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.547499530846845</v>
+        <v>2.689889462955829</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.068251553308791</v>
+        <v>-5.826296907813022</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.7363973005483913</v>
+        <v>0.8331791587466988</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.006080790191919</v>
+        <v>-0.7687642366769458</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.560405872070504</v>
+        <v>2.702795804179488</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.173841543081895</v>
+        <v>-5.931886897586127</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5661853750399306</v>
+        <v>0.6629672332382381</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.111670779965024</v>
+        <v>-0.8743542264500501</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.369075948607422</v>
+        <v>2.511465880716407</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.192576445200492</v>
+        <v>-5.950621799704724</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.6072357560695782</v>
+        <v>0.7040176142678858</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.111670779965024</v>
+        <v>-0.8743542264500501</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.417620290484509</v>
+        <v>2.560010222593493</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.915838270529679</v>
+        <v>-5.673883625033911</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.7213100379238981</v>
+        <v>0.8180918961222057</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.9298541188550978</v>
+        <v>-0.6925375653401243</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.530089299136459</v>
+        <v>2.672479231245443</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.788945864094609</v>
+        <v>-5.546991218598841</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.7633530142444482</v>
+        <v>0.8601348724427558</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8029617124200279</v>
+        <v>-0.5656451589050544</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.597510756744023</v>
+        <v>2.739900688853007</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.601358356184683</v>
+        <v>-5.359403710688914</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.8314274053133257</v>
+        <v>0.9282092635116328</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8029617124200279</v>
+        <v>-0.5656451589050544</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.59055014464893</v>
+        <v>2.732940076757914</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.359209962730825</v>
+        <v>-5.117255317235056</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.9427491170760121</v>
+        <v>1.039530975274319</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8029617124200279</v>
+        <v>-0.5656451589050544</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.605012499030073</v>
+        <v>2.747402431139057</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.295980590962476</v>
+        <v>-5.054025945466708</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.9625729862425461</v>
+        <v>1.059354844440854</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8029617124200279</v>
+        <v>-0.5656451589050544</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.599544619489268</v>
+        <v>2.741934551598252</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.10949289858547</v>
+        <v>-4.867538253089702</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.034666157203926</v>
+        <v>1.131448015402233</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.6164740200430217</v>
+        <v>-0.3791574665280482</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.708935328926048</v>
+        <v>2.851325261035032</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.088343699682027</v>
+        <v>-4.846389054186258</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.050826815002628</v>
+        <v>1.147608673200936</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.5953248211395783</v>
+        <v>-0.3580082676246048</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.72932582650544</v>
+        <v>2.871715758614424</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.844578257698583</v>
+        <v>-4.602623612202814</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.144113700143057</v>
+        <v>1.240895558341364</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.5953248211395783</v>
+        <v>-0.3580082676246048</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.725106534852491</v>
+        <v>2.867496466961475</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.580550190505322</v>
+        <v>-4.338595545009554</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.251849240940377</v>
+        <v>1.348631099138685</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3934594223236247</v>
+        <v>-0.1561428688086512</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.848350088062078</v>
+        <v>2.990740020171063</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.330699796556248</v>
+        <v>-4.088745151060479</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.344531473503709</v>
+        <v>1.441313331702017</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3934594223236247</v>
+        <v>-0.1561428688086512</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.841092163045781</v>
+        <v>2.983482095154765</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.027132307552269</v>
+        <v>-3.785177662056501</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.469557592625949</v>
+        <v>1.566339450824257</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3934594223236247</v>
+        <v>-0.1561428688086512</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.844691286566429</v>
+        <v>2.987081218675414</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.953652398700255</v>
+        <v>-3.711697753204486</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.512277062221309</v>
+        <v>1.609058920419616</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3199795134716104</v>
+        <v>-0.08266295995663686</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.902106737932192</v>
+        <v>3.044496670041176</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.728619399031432</v>
+        <v>-3.486664753535663</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.601310739705135</v>
+        <v>1.698092597903442</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.09494651380278751</v>
+        <v>0.142370039712186</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.036147015349782</v>
+        <v>3.178536947458767</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.513985021395025</v>
+        <v>-3.272030375899257</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.691859291814015</v>
+        <v>1.788641150012322</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1196878638336193</v>
+        <v>0.3570044173485928</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.169622442985944</v>
+        <v>3.312012375094928</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,13 +45803,13 @@
         <v>3.081384075377701</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.513985021395025</v>
+        <v>-3.272030375899257</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.691859291814015</v>
+        <v>1.788641150012322</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1196878638336193</v>
+        <v>0.3570044173485928</v>
       </c>
       <c r="G1924" t="n">
         <v>3.074447872364069</v>

--- a/tame_output/ON/bt/strategyON_20240404.xlsx
+++ b/tame_output/ON/bt/strategyON_20240404.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.7%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.6%</t>
+          <t>130.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.7%</t>
+          <t>-69.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>500.1%</t>
+          <t>500.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-488.8%</t>
+          <t>-485.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>110.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-197.4%</t>
+          <t>-198.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-138.6%</t>
+          <t>-116.7%</t>
         </is>
       </c>
     </row>
@@ -45800,19 +45800,19 @@
         <v>3.735720826754782</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.081384075377701</v>
+        <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.272030375899257</v>
+        <v>-3.241697873002388</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.788641150012322</v>
+        <v>1.781968409954865</v>
       </c>
       <c r="F1924" t="n">
         <v>0.3570044173485928</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.074447872364069</v>
+        <v>3.293206633878724</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240404.xlsx
+++ b/tame_output/ON/bt/strategyON_20240404.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>500.2%</t>
+          <t>496.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-485.7%</t>
+          <t>-489.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-198.0%</t>
+          <t>-199.2%</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-116.7%</t>
+          <t>-116.5%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097825</v>
+        <v>3.341378723097826</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094121</v>
+        <v>3.374439043094122</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199291</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969599</v>
+        <v>3.4246333549696</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923093</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297755</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.447750501317622</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737176</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341318</v>
+        <v>3.503170282341319</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425329</v>
+        <v>3.72857435442533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702414</v>
+        <v>3.747699084702415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.098802650364638</v>
+        <v>-9.361070378419001</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4741409714163676</v>
+        <v>-0.5790480626381127</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.508621875068816</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.76631350390623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.83156084949624</v>
+        <v>-9.093828577550603</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3690788115683823</v>
+        <v>-0.4739859027901274</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.508621875068816</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.555751686095755</v>
+        <v>-8.818019414150118</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2590554611816489</v>
+        <v>-0.3639625524033945</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.419602566790083</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567245</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.286684098328776</v>
+        <v>-8.548951826383139</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1507599199293637</v>
+        <v>-0.2556670111511088</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.150534979023103</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.022624160005979</v>
+        <v>-8.284891888060342</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.058396260761997</v>
+        <v>-0.1633033519837421</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.886475040700307</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.31554453650114</v>
+        <v>-7.577812264555503</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2216485549796374</v>
+        <v>0.1167414637578923</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.886475040700307</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.065903506515189</v>
+        <v>-7.328171234569552</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.3218485908618596</v>
+        <v>0.2169414996401144</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.636834010714356</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-6.811361607174113</v>
+        <v>-7.073629335228476</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.4230321718190466</v>
+        <v>0.3181250805973015</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.38229211137328</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.577880384944515</v>
+        <v>-6.840148112998878</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.5243490895487382</v>
+        <v>0.419441998326993</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.148810889143681</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.398171854800642</v>
+        <v>-6.660439582855005</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.5933402912933281</v>
+        <v>0.488433200071583</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.091639384980985</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.265896381169756</v>
+        <v>-6.528164109224119</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.6416179674927096</v>
+        <v>0.5367108762709645</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.9593639113500987</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.075296706496603</v>
+        <v>-6.337564434550966</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.7206728980496075</v>
+        <v>0.6157658068278624</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.7687642366769458</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-5.826296907813022</v>
+        <v>-6.088564635867385</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.8331791587466988</v>
+        <v>0.7282720675249537</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.7687642366769458</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-5.931886897586127</v>
+        <v>-6.19415462564049</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.6629672332382381</v>
+        <v>0.558060142016493</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.8743542264500501</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-5.950621799704724</v>
+        <v>-6.212889527759087</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.7040176142678858</v>
+        <v>0.5991105230461407</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.8743542264500501</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-5.673883625033911</v>
+        <v>-5.936151353088274</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.8180918961222057</v>
+        <v>0.7131848049004605</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.6925375653401243</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-5.546991218598841</v>
+        <v>-5.809258946653204</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.8601348724427558</v>
+        <v>0.7552277812210102</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5656451589050544</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-5.359403710688914</v>
+        <v>-5.621671438743277</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.9282092635116328</v>
+        <v>0.8233021722898877</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5656451589050544</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.117255317235056</v>
+        <v>-5.379523045289419</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.039530975274319</v>
+        <v>0.934623884052574</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5656451589050544</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192815</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.054025945466708</v>
+        <v>-5.316293673521071</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.059354844440854</v>
+        <v>0.9544477532191085</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5656451589050544</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-4.867538253089702</v>
+        <v>-5.129805981144065</v>
       </c>
       <c r="E1915" t="n">
-        <v>1.131448015402233</v>
+        <v>1.026540924180488</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.3791574665280482</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-4.846389054186258</v>
+        <v>-5.108656782240621</v>
       </c>
       <c r="E1916" t="n">
-        <v>1.147608673200936</v>
+        <v>1.042701581979191</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3580082676246048</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-4.602623612202814</v>
+        <v>-4.864891340257177</v>
       </c>
       <c r="E1917" t="n">
-        <v>1.240895558341364</v>
+        <v>1.135988467119619</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3580082676246048</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-4.338595545009554</v>
+        <v>-4.600863273063917</v>
       </c>
       <c r="E1918" t="n">
-        <v>1.348631099138685</v>
+        <v>1.243724007916939</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.1561428688086512</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.088745151060479</v>
+        <v>-4.351012879114842</v>
       </c>
       <c r="E1919" t="n">
-        <v>1.441313331702017</v>
+        <v>1.336406240480271</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.1561428688086512</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-3.785177662056501</v>
+        <v>-4.047445390110863</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.566339450824257</v>
+        <v>1.461432359602512</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.1561428688086512</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-3.711697753204486</v>
+        <v>-3.973965481258849</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.609058920419616</v>
+        <v>1.504151829197871</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.08266295995663686</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-3.486664753535663</v>
+        <v>-3.748932481590026</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.698092597903442</v>
+        <v>1.593185506681697</v>
       </c>
       <c r="F1922" t="n">
         <v>0.142370039712186</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353078</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-3.272030375899257</v>
+        <v>-3.534298103953619</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.788641150012322</v>
+        <v>1.683734058790577</v>
       </c>
       <c r="F1923" t="n">
         <v>0.3570044173485928</v>
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.735720826754782</v>
+        <v>3.413501838641404</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.079003983469568</v>
+        <v>3.081384075377701</v>
       </c>
       <c r="D1924" t="n">
-        <v>-3.241697873002388</v>
+        <v>-3.276340044819202</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.781968409954865</v>
+        <v>1.770491633136273</v>
       </c>
       <c r="F1924" t="n">
         <v>0.3570044173485928</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.293206633878724</v>
+        <v>3.295586725786857</v>
       </c>
     </row>
   </sheetData>
